--- a/Employee_Reports_wi48/Roderick Cailao Amar Q0480.xlsx
+++ b/Employee_Reports_wi48/Roderick Cailao Amar Q0480.xlsx
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -630,11 +630,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -679,11 +679,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -728,11 +728,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -777,11 +777,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -792,53 +792,53 @@
       <c r="K7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Weight scales (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-M-013</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>12-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>12-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>08-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>632</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -875,11 +875,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -924,11 +924,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1071,11 +1071,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1120,11 +1120,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1169,11 +1169,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1218,11 +1218,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1267,11 +1267,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1316,11 +1316,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1365,11 +1365,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1537,11 +1537,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1586,11 +1586,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1635,11 +1635,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>-95</v>
+        <v>-98</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1658,9 +1658,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>18-Mar-2025</t>
@@ -1672,11 +1684,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1721,11 +1733,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1770,11 +1782,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1819,11 +1831,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1868,11 +1880,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1917,11 +1929,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1954,11 +1966,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1991,11 +2003,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2040,11 +2052,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2077,11 +2089,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2114,11 +2126,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2151,11 +2163,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2188,11 +2200,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2225,11 +2237,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2967,7 +2979,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2996,7 +3008,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3025,7 +3037,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3054,7 +3066,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3083,7 +3095,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3112,7 +3124,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3141,7 +3153,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7948</v>
+        <v>7945</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3170,7 +3182,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3199,7 +3211,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3228,7 +3240,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7948</v>
+        <v>7945</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3257,7 +3269,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7953</v>
+        <v>7950</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
